--- a/resource/groundTruths/architecture/CF_M04_ground_truth_architecture.xlsx
+++ b/resource/groundTruths/architecture/CF_M04_ground_truth_architecture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/architecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56B5EF6-5CBF-0F46-9B1A-E8E6C7EC5020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936A71C8-101E-1046-8868-E37352CF40CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" xr2:uid="{3A3C78BF-C5C1-CB4F-9B14-1410E0995AFF}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" activeTab="1" xr2:uid="{3A3C78BF-C5C1-CB4F-9B14-1410E0995AFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Architectural Units" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="122">
   <si>
     <t>Document ID</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>Communication between the front-end and the back-end is done through a REST API, using JSON format messages for both requests and responses.</t>
+  </si>
+  <si>
+    <t>Fixed Type</t>
   </si>
 </sst>
 </file>
@@ -784,10 +787,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BFFF875-5AA9-7242-91BC-C9913F8AB7F1}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,8 +812,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -830,7 +836,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -853,7 +859,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -876,7 +882,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -896,7 +902,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -919,7 +925,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -942,7 +948,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -965,7 +971,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -988,7 +994,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -1011,7 +1017,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1031,7 +1037,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1054,7 +1060,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1094,7 +1100,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1114,7 +1120,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -1433,10 +1439,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C14E62F0-CEAA-B04F-884E-C31EA83FC71C}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1458,8 +1464,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1482,7 +1491,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1505,7 +1514,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1528,7 +1537,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1551,7 +1560,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1574,7 +1583,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1597,7 +1606,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1620,7 +1629,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
